--- a/templates/1_题目分布表模板.xlsx
+++ b/templates/1_题目分布表模板.xlsx
@@ -132,14 +132,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="20">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -595,148 +588,148 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -1118,10 +1111,10 @@
         <v>5</v>
       </c>
       <c r="C4">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1132,10 +1125,10 @@
         <v>6</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1146,10 +1139,10 @@
         <v>7</v>
       </c>
       <c r="C6">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1160,10 +1153,10 @@
         <v>8</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1174,10 +1167,10 @@
         <v>10</v>
       </c>
       <c r="C8">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1188,10 +1181,10 @@
         <v>11</v>
       </c>
       <c r="C9">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D9">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1202,10 +1195,10 @@
         <v>12</v>
       </c>
       <c r="C10">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1216,10 +1209,10 @@
         <v>14</v>
       </c>
       <c r="C11">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1230,10 +1223,10 @@
         <v>15</v>
       </c>
       <c r="C12">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1244,10 +1237,10 @@
         <v>16</v>
       </c>
       <c r="C13">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1258,10 +1251,10 @@
         <v>17</v>
       </c>
       <c r="C14">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D14">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1272,10 +1265,10 @@
         <v>18</v>
       </c>
       <c r="C15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D15">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -1286,10 +1279,10 @@
         <v>19</v>
       </c>
       <c r="C16">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="18" spans="1:3">
@@ -1311,7 +1304,7 @@
         <v>24</v>
       </c>
       <c r="C19">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="20" spans="1:3">
@@ -1322,7 +1315,7 @@
         <v>25</v>
       </c>
       <c r="C20">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="21" spans="1:3">
@@ -1333,7 +1326,7 @@
         <v>26</v>
       </c>
       <c r="C21">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="22" spans="1:3">
@@ -1344,7 +1337,7 @@
         <v>24</v>
       </c>
       <c r="C22">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23" spans="1:3">
@@ -1355,7 +1348,7 @@
         <v>25</v>
       </c>
       <c r="C23">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:3">
@@ -1366,7 +1359,7 @@
         <v>26</v>
       </c>
       <c r="C24">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="25" spans="1:3">
@@ -1377,7 +1370,7 @@
         <v>24</v>
       </c>
       <c r="C25">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="26" spans="1:3">
@@ -1388,7 +1381,7 @@
         <v>25</v>
       </c>
       <c r="C26">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27" spans="1:3">
@@ -1399,7 +1392,7 @@
         <v>26</v>
       </c>
       <c r="C27">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="28" spans="1:3">
@@ -1410,7 +1403,7 @@
         <v>24</v>
       </c>
       <c r="C28">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="29" spans="1:3">
@@ -1421,7 +1414,7 @@
         <v>25</v>
       </c>
       <c r="C29">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:3">
@@ -1432,7 +1425,7 @@
         <v>26</v>
       </c>
       <c r="C30">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="31" spans="1:3">
@@ -1443,7 +1436,7 @@
         <v>24</v>
       </c>
       <c r="C31">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="32" spans="1:3">
@@ -1454,7 +1447,7 @@
         <v>25</v>
       </c>
       <c r="C32">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33" spans="1:3">
@@ -1465,7 +1458,7 @@
         <v>26</v>
       </c>
       <c r="C33">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
